--- a/data/trans_orig/IP07A05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A05-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27952</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35104</t>
+          <t>34580</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40488</t>
+          <t>39951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59301</t>
+          <t>58456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32403</t>
+          <t>32093</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38933</t>
+          <t>39166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53481</t>
+          <t>53898</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75064</t>
+          <t>75510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94295</t>
+          <t>95287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,79%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35780</t>
+          <t>35486</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51883</t>
+          <t>51356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33922</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49237</t>
+          <t>48264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74037</t>
+          <t>72848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96388</t>
+          <t>95944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>40621</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55395</t>
+          <t>56092</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>37465</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51889</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82172</t>
+          <t>82345</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103086</t>
+          <t>104887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>15783</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>27805</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17607</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29026</t>
+          <t>29594</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>20282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31862</t>
+          <t>32996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41287</t>
+          <t>40931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57506</t>
+          <t>58155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24062</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36846</t>
+          <t>36223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25558</t>
+          <t>25702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37974</t>
+          <t>38584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54378</t>
+          <t>52602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71101</t>
+          <t>71510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29517</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46304</t>
+          <t>46417</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>36219</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>52506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71160</t>
+          <t>70660</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93504</t>
+          <t>93232</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,77%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36447</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53415</t>
+          <t>52813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39864</t>
+          <t>39093</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56644</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81294</t>
+          <t>81648</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>105099</t>
+          <t>104801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,82%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>726</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7316</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111731</t>
+          <t>111968</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>140189</t>
+          <t>139968</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>125323</t>
+          <t>125772</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>154672</t>
+          <t>154830</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>246176</t>
+          <t>245938</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>286825</t>
+          <t>285827</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>147848</t>
+          <t>146931</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>177700</t>
+          <t>177254</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155550</t>
+          <t>156254</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>184939</t>
+          <t>184719</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>312933</t>
+          <t>312506</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>353106</t>
+          <t>352604</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36540</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>47586</t>
+          <t>47508</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>71228</t>
+          <t>71262</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13538</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18677</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32407</t>
+          <t>32537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>38404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56899</t>
+          <t>57081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29667</t>
+          <t>30415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>43402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34076</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48350</t>
+          <t>48328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68120</t>
+          <t>69182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87813</t>
+          <t>88286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,84%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30819</t>
+          <t>30619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>46136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>26899</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41984</t>
+          <t>42043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60893</t>
+          <t>61012</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81911</t>
+          <t>83508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,97%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42516</t>
+          <t>42253</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58070</t>
+          <t>57883</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59394</t>
+          <t>59570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91842</t>
+          <t>90219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114436</t>
+          <t>113329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,31%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>16821</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29103</t>
+          <t>29408</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27502</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>40319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46491</t>
+          <t>47551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65295</t>
+          <t>65367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32191</t>
+          <t>31982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45194</t>
+          <t>45059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20575</t>
+          <t>21176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33840</t>
+          <t>34090</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57218</t>
+          <t>57435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>76664</t>
+          <t>75391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13892</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38072</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>24085</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>39325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50802</t>
+          <t>50782</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72413</t>
+          <t>72491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>42603</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58834</t>
+          <t>59289</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>42197</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58497</t>
+          <t>58227</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>88788</t>
+          <t>89728</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112899</t>
+          <t>111994</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>23933</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99302</t>
+          <t>98295</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>127265</t>
+          <t>126384</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>110246</t>
+          <t>110034</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>139237</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>217769</t>
+          <t>218049</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>258594</t>
+          <t>258627</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>162906</t>
+          <t>162873</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>192042</t>
+          <t>192118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>154927</t>
+          <t>155316</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>186082</t>
+          <t>185221</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>325838</t>
+          <t>326822</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>367315</t>
+          <t>367572</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>34540</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>39093</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>62300</t>
+          <t>61998</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>24082</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39053</t>
+          <t>38685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28210</t>
+          <t>28321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43526</t>
+          <t>43089</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56874</t>
+          <t>57445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78826</t>
+          <t>77938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27598</t>
+          <t>27626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41937</t>
+          <t>42167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26553</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41550</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57317</t>
+          <t>57855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78981</t>
+          <t>78825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>815</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41533</t>
+          <t>42320</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57667</t>
+          <t>58824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46477</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63543</t>
+          <t>63670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93469</t>
+          <t>93745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116656</t>
+          <t>117380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39366</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55628</t>
+          <t>55419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34813</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50907</t>
+          <t>51373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80032</t>
+          <t>78044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103757</t>
+          <t>102231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17334</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -9037,62 +9037,62 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7370</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2339</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>672</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7042</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6635</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2339</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6370</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>30297</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42778</t>
+          <t>43402</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>26679</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41118</t>
+          <t>41621</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60582</t>
+          <t>60978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81173</t>
+          <t>80639</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,88%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>20339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33964</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32032</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47627</t>
+          <t>46354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56746</t>
+          <t>57491</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75964</t>
+          <t>77337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>519</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>29895</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47557</t>
+          <t>47687</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>37499</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54824</t>
+          <t>54507</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>72205</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96459</t>
+          <t>97109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46540</t>
+          <t>45821</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>64163</t>
+          <t>64695</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40165</t>
+          <t>39725</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>56588</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>91587</t>
+          <t>91932</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>115889</t>
+          <t>117796</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>10927</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25228</t>
+          <t>25982</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>140380</t>
+          <t>141120</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>171105</t>
+          <t>171141</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>156566</t>
+          <t>155334</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>186644</t>
+          <t>187166</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>307394</t>
+          <t>306581</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>351236</t>
+          <t>350560</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>150512</t>
+          <t>150258</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>183954</t>
+          <t>180635</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>148297</t>
+          <t>148238</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>179901</t>
+          <t>180689</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>306227</t>
+          <t>307059</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>351236</t>
+          <t>351845</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>35710</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>35039</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>56341</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
